--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Priority-Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF03BE0-CF81-4068-B56C-2FD1C87D9EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5BE2B-C250-447A-B06B-6E399DC1BA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3246" uniqueCount="97">
   <si>
     <t>Company Name</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>Rashaad Moore</t>
+  </si>
+  <si>
+    <t>Speed Mangement-C</t>
   </si>
 </sst>
 </file>
@@ -18528,16 +18531,45 @@
       </c>
     </row>
     <row r="619" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F619" s="2"/>
-      <c r="G619" s="1"/>
-      <c r="H619" s="2"/>
-      <c r="I619" s="1"/>
+      <c r="B619" t="s">
+        <v>40</v>
+      </c>
+      <c r="C619">
+        <v>4881</v>
+      </c>
+      <c r="D619" t="s">
+        <v>44</v>
+      </c>
+      <c r="E619" t="s">
+        <v>44</v>
+      </c>
+      <c r="F619" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G619" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H619" s="2">
+        <v>2.974537037037037E-2</v>
+      </c>
+      <c r="I619" s="1">
+        <v>46190.628819444442</v>
+      </c>
+      <c r="J619">
+        <v>0</v>
+      </c>
+      <c r="K619" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="620" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F620" s="2"/>
       <c r="G620" s="1"/>
       <c r="H620" s="2"/>
       <c r="I620" s="1"/>
+      <c r="K620" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="621" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F621" s="2"/>
